--- a/Condo_IV_Reserve_Plan.xlsx
+++ b/Condo_IV_Reserve_Plan.xlsx
@@ -2259,7 +2259,7 @@
         <v/>
       </c>
       <c r="C5" s="15">
-        <f>'Fund Summary'!$C$12</f>
+        <f>IF('Fund Summary'!$D$12&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12)</f>
         <v/>
       </c>
       <c r="D5" s="15" t="n">
@@ -2291,7 +2291,7 @@
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>C5*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F5&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^1)</f>
         <v/>
       </c>
       <c r="D6" s="15" t="n">
@@ -2323,7 +2323,7 @@
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>C6*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F6&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^2)</f>
         <v/>
       </c>
       <c r="D7" s="15" t="n">
@@ -2355,7 +2355,7 @@
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>C7*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F7&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^3)</f>
         <v/>
       </c>
       <c r="D8" s="15" t="n">
@@ -2387,7 +2387,7 @@
         <v/>
       </c>
       <c r="C9" s="15">
-        <f>C8*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F8&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^4)</f>
         <v/>
       </c>
       <c r="D9" s="15" t="n">
@@ -2419,7 +2419,7 @@
         <v/>
       </c>
       <c r="C10" s="15">
-        <f>C9*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F9&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^5)</f>
         <v/>
       </c>
       <c r="D10" s="15" t="n">
@@ -2451,7 +2451,7 @@
         <v/>
       </c>
       <c r="C11" s="15">
-        <f>C10*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F10&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^6)</f>
         <v/>
       </c>
       <c r="D11" s="15" t="n">
@@ -2483,7 +2483,7 @@
         <v/>
       </c>
       <c r="C12" s="15">
-        <f>C11*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F11&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^7)</f>
         <v/>
       </c>
       <c r="D12" s="15" t="n">
@@ -2515,7 +2515,7 @@
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>C12*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F12&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^8)</f>
         <v/>
       </c>
       <c r="D13" s="15" t="n">
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="C14" s="15">
-        <f>C13*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F13&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^9)</f>
         <v/>
       </c>
       <c r="D14" s="15" t="n">
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="C15" s="15">
-        <f>C14*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F14&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^10)</f>
         <v/>
       </c>
       <c r="D15" s="15" t="n">
@@ -2611,7 +2611,7 @@
         <v/>
       </c>
       <c r="C16" s="15">
-        <f>C15*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F15&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^11)</f>
         <v/>
       </c>
       <c r="D16" s="15" t="n">
@@ -2643,7 +2643,7 @@
         <v/>
       </c>
       <c r="C17" s="15">
-        <f>C16*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F16&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^12)</f>
         <v/>
       </c>
       <c r="D17" s="15" t="n">
@@ -2675,7 +2675,7 @@
         <v/>
       </c>
       <c r="C18" s="15">
-        <f>C17*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F17&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^13)</f>
         <v/>
       </c>
       <c r="D18" s="15" t="n">
@@ -2707,7 +2707,7 @@
         <v/>
       </c>
       <c r="C19" s="15">
-        <f>C18*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F18&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^14)</f>
         <v/>
       </c>
       <c r="D19" s="15" t="n">
@@ -2739,7 +2739,7 @@
         <v/>
       </c>
       <c r="C20" s="15">
-        <f>C19*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F19&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^15)</f>
         <v/>
       </c>
       <c r="D20" s="15" t="n">
@@ -2771,7 +2771,7 @@
         <v/>
       </c>
       <c r="C21" s="15">
-        <f>C20*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F20&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^16)</f>
         <v/>
       </c>
       <c r="D21" s="15" t="n">
@@ -2803,7 +2803,7 @@
         <v/>
       </c>
       <c r="C22" s="15">
-        <f>C21*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F21&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^17)</f>
         <v/>
       </c>
       <c r="D22" s="15" t="n">
@@ -2835,7 +2835,7 @@
         <v/>
       </c>
       <c r="C23" s="15">
-        <f>C22*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F22&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^18)</f>
         <v/>
       </c>
       <c r="D23" s="15" t="n">
@@ -2867,7 +2867,7 @@
         <v/>
       </c>
       <c r="C24" s="15">
-        <f>C23*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F23&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^19)</f>
         <v/>
       </c>
       <c r="D24" s="15" t="n">
@@ -2899,7 +2899,7 @@
         <v/>
       </c>
       <c r="C25" s="15">
-        <f>C24*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F24&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^20)</f>
         <v/>
       </c>
       <c r="D25" s="15" t="n">
@@ -2931,7 +2931,7 @@
         <v/>
       </c>
       <c r="C26" s="15">
-        <f>C25*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F25&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^21)</f>
         <v/>
       </c>
       <c r="D26" s="15" t="n">
@@ -2963,7 +2963,7 @@
         <v/>
       </c>
       <c r="C27" s="15">
-        <f>C26*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F26&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^22)</f>
         <v/>
       </c>
       <c r="D27" s="15" t="n">
@@ -2995,7 +2995,7 @@
         <v/>
       </c>
       <c r="C28" s="15">
-        <f>C27*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F27&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^23)</f>
         <v/>
       </c>
       <c r="D28" s="15" t="n">
@@ -3027,7 +3027,7 @@
         <v/>
       </c>
       <c r="C29" s="15">
-        <f>C28*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F28&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^24)</f>
         <v/>
       </c>
       <c r="D29" s="15" t="n">
@@ -4082,7 +4082,7 @@
         <v/>
       </c>
       <c r="C5" s="15">
-        <f>'Fund Summary'!$C$14</f>
+        <f>IF('Fund Summary'!$D$14&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14)</f>
         <v/>
       </c>
       <c r="D5" s="15" t="n">
@@ -4114,7 +4114,7 @@
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>C5*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F5&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^1)</f>
         <v/>
       </c>
       <c r="D6" s="15" t="n">
@@ -4146,7 +4146,7 @@
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>C6*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F6&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^2)</f>
         <v/>
       </c>
       <c r="D7" s="15" t="n">
@@ -4178,7 +4178,7 @@
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>C7*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F7&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^3)</f>
         <v/>
       </c>
       <c r="D8" s="15" t="n">
@@ -4210,7 +4210,7 @@
         <v/>
       </c>
       <c r="C9" s="15">
-        <f>C8*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F8&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^4)</f>
         <v/>
       </c>
       <c r="D9" s="15" t="n">
@@ -4242,7 +4242,7 @@
         <v/>
       </c>
       <c r="C10" s="15">
-        <f>C9*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F9&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^5)</f>
         <v/>
       </c>
       <c r="D10" s="15" t="n">
@@ -4274,7 +4274,7 @@
         <v/>
       </c>
       <c r="C11" s="15">
-        <f>C10*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F10&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^6)</f>
         <v/>
       </c>
       <c r="D11" s="15" t="n">
@@ -4306,7 +4306,7 @@
         <v/>
       </c>
       <c r="C12" s="15">
-        <f>C11*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F11&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^7)</f>
         <v/>
       </c>
       <c r="D12" s="15" t="n">
@@ -4338,7 +4338,7 @@
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>C12*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F12&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^8)</f>
         <v/>
       </c>
       <c r="D13" s="15" t="n">
@@ -4370,7 +4370,7 @@
         <v/>
       </c>
       <c r="C14" s="15">
-        <f>C13*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F13&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^9)</f>
         <v/>
       </c>
       <c r="D14" s="15" t="n">
@@ -4402,7 +4402,7 @@
         <v/>
       </c>
       <c r="C15" s="15">
-        <f>C14*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F14&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^10)</f>
         <v/>
       </c>
       <c r="D15" s="15" t="n">
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="C16" s="15">
-        <f>C15*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F15&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^11)</f>
         <v/>
       </c>
       <c r="D16" s="15" t="n">
@@ -4466,7 +4466,7 @@
         <v/>
       </c>
       <c r="C17" s="15">
-        <f>C16*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F16&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^12)</f>
         <v/>
       </c>
       <c r="D17" s="15" t="n">
@@ -4498,7 +4498,7 @@
         <v/>
       </c>
       <c r="C18" s="15">
-        <f>C17*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F17&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^13)</f>
         <v/>
       </c>
       <c r="D18" s="15" t="n">
@@ -4530,7 +4530,7 @@
         <v/>
       </c>
       <c r="C19" s="15">
-        <f>C18*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F18&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^14)</f>
         <v/>
       </c>
       <c r="D19" s="15" t="n">
@@ -4562,7 +4562,7 @@
         <v/>
       </c>
       <c r="C20" s="15">
-        <f>C19*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F19&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^15)</f>
         <v/>
       </c>
       <c r="D20" s="15" t="n">
@@ -4594,7 +4594,7 @@
         <v/>
       </c>
       <c r="C21" s="15">
-        <f>C20*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F20&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^16)</f>
         <v/>
       </c>
       <c r="D21" s="15" t="n">
@@ -4626,7 +4626,7 @@
         <v/>
       </c>
       <c r="C22" s="15">
-        <f>C21*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F21&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^17)</f>
         <v/>
       </c>
       <c r="D22" s="15" t="n">
@@ -4658,7 +4658,7 @@
         <v/>
       </c>
       <c r="C23" s="15">
-        <f>C22*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F22&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^18)</f>
         <v/>
       </c>
       <c r="D23" s="15" t="n">
@@ -4690,7 +4690,7 @@
         <v/>
       </c>
       <c r="C24" s="15">
-        <f>C23*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F23&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^19)</f>
         <v/>
       </c>
       <c r="D24" s="15" t="n">
@@ -4722,7 +4722,7 @@
         <v/>
       </c>
       <c r="C25" s="15">
-        <f>C24*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F24&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^20)</f>
         <v/>
       </c>
       <c r="D25" s="15" t="n">
@@ -4754,7 +4754,7 @@
         <v/>
       </c>
       <c r="C26" s="15">
-        <f>C25*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F25&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^21)</f>
         <v/>
       </c>
       <c r="D26" s="15" t="n">
@@ -4786,7 +4786,7 @@
         <v/>
       </c>
       <c r="C27" s="15">
-        <f>C26*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F26&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^22)</f>
         <v/>
       </c>
       <c r="D27" s="15" t="n">
@@ -4818,7 +4818,7 @@
         <v/>
       </c>
       <c r="C28" s="15">
-        <f>C27*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F27&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^23)</f>
         <v/>
       </c>
       <c r="D28" s="15" t="n">
@@ -4850,7 +4850,7 @@
         <v/>
       </c>
       <c r="C29" s="15">
-        <f>C28*(1+'Fund Summary'!$B$7)</f>
+        <f>IF(F28&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^24)</f>
         <v/>
       </c>
       <c r="D29" s="15" t="n">

--- a/Condo_IV_Reserve_Plan.xlsx
+++ b/Condo_IV_Reserve_Plan.xlsx
@@ -67,7 +67,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -134,18 +134,6 @@
         <bgColor rgb="009B57A0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00636363"/>
-        <bgColor rgb="00636363"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EB7E30"/>
-        <bgColor rgb="00EB7E30"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -165,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -208,8 +196,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -363,12 +349,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Expenditure Chart'!$E$3:$E$13</f>
+              <f>'Expenditure Chart'!$E$3:$E$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Expenditure Chart'!$F$3:$F$13</f>
+              <f>'Expenditure Chart'!$F$3:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -390,12 +376,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Expenditure Chart'!$E$3:$E$13</f>
+              <f>'Expenditure Chart'!$E$3:$E$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Expenditure Chart'!$G$3:$G$13</f>
+              <f>'Expenditure Chart'!$G$3:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -417,12 +403,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Expenditure Chart'!$E$3:$E$13</f>
+              <f>'Expenditure Chart'!$E$3:$E$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Expenditure Chart'!$H$3:$H$13</f>
+              <f>'Expenditure Chart'!$H$3:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -444,12 +430,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Expenditure Chart'!$E$3:$E$13</f>
+              <f>'Expenditure Chart'!$E$3:$E$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Expenditure Chart'!$I$3:$I$13</f>
+              <f>'Expenditure Chart'!$I$3:$I$12</f>
             </numRef>
           </val>
         </ser>
@@ -471,12 +457,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Expenditure Chart'!$E$3:$E$13</f>
+              <f>'Expenditure Chart'!$E$3:$E$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Expenditure Chart'!$J$3:$J$13</f>
+              <f>'Expenditure Chart'!$J$3:$J$12</f>
             </numRef>
           </val>
         </ser>
@@ -498,12 +484,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Expenditure Chart'!$E$3:$E$13</f>
+              <f>'Expenditure Chart'!$E$3:$E$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Expenditure Chart'!$K$3:$K$13</f>
+              <f>'Expenditure Chart'!$K$3:$K$12</f>
             </numRef>
           </val>
         </ser>
@@ -525,12 +511,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Expenditure Chart'!$E$3:$E$13</f>
+              <f>'Expenditure Chart'!$E$3:$E$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Expenditure Chart'!$L$3:$L$13</f>
+              <f>'Expenditure Chart'!$L$3:$L$12</f>
             </numRef>
           </val>
         </ser>
@@ -552,66 +538,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Expenditure Chart'!$E$3:$E$13</f>
+              <f>'Expenditure Chart'!$E$3:$E$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Expenditure Chart'!$M$3:$M$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <tx>
-            <strRef>
-              <f>'Expenditure Chart'!N2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="636363"/>
-            </a:solidFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Expenditure Chart'!$E$3:$E$13</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Expenditure Chart'!$N$3:$N$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <tx>
-            <strRef>
-              <f>'Expenditure Chart'!O2</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="EB7E30"/>
-            </a:solidFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Expenditure Chart'!$E$3:$E$13</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Expenditure Chart'!$O$3:$O$13</f>
+              <f>'Expenditure Chart'!$M$3:$M$12</f>
             </numRef>
           </val>
         </ser>
@@ -687,7 +619,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="12960000" cy="7200000"/>
@@ -998,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E83"/>
+  <dimension ref="B1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1109,7 +1041,7 @@
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Total replacement cost (current dollars): $3,451,433</t>
+          <t>Total replacement cost (current dollars): $3,191,785</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1128,7 @@
     <row r="33">
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>1. Emergency Reserve — self-funded buffer to replace the worst-case building.</t>
+          <t>1. Emergency Reserve — self-funded buffer for uninsured structural &amp; shortfall exposure — deductible on HOA.</t>
         </is>
       </c>
     </row>
@@ -1402,24 +1334,24 @@
     <row r="63">
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Asphalt Driveways (Condo IV share)</t>
+          <t>Deck Framing &amp; Footings, Wood (Condo IV share)</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>254562</v>
+        <v>64750</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>2036</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Deck Framing &amp; Footings, Wood (Condo IV share)</t>
+          <t>Deck Boards (surface), Wood (Condo IV share)</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>64750</v>
+        <v>56657</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>2033</v>
@@ -1428,195 +1360,139 @@
     <row r="65">
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Deck Boards (surface), Wood (Condo IV share)</t>
+          <t>Deck Railings &amp; Balusters, Wood (Condo IV share) (safety)</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>56657</v>
+        <v>40469</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>2033</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Deck Railings &amp; Balusters, Wood (Condo IV share) (safety)</t>
+          <t>Deck Replacement, Composite (Condo IV share)</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
-        <v>40469</v>
+        <v>132444</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2027</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Deck Replacement, Composite (Condo IV share)</t>
+          <t>Chimney Chase Covers (Condo IV share)</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>132444</v>
+        <v>125160</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>2053</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Chimney Chase Covers (Condo IV share)</t>
+          <t>Entry Stoops — Concrete Replacement</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
-        <v>125160</v>
+        <v>196000</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Concrete Sidewalks (Condo IV share)</t>
+          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5086</v>
+        <v>29400</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>2033</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Entry Stoops — Concrete Replacement</t>
+          <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
-        <v>196000</v>
+        <v>15000</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="n">
-        <v>29400</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="n">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Items NOT Included (Budget Separately)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>The following items from the Falcon 2022 report are NOT in the Becht 2026 study and are therefore NOT included in this funding schedule. Consider budgeting for these items separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Falcon Est. Cost</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Retaining Wall, Wood Tie Wells</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="D72" s="3" t="n">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Items NOT Included (Budget Separately)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>The following items from the Falcon 2022 report are NOT in the Becht 2026 study and are therefore NOT included in this funding schedule. Consider budgeting for these items separately.</t>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Structural/safety; Falcon estimated $15,000</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>Falcon Est. Cost</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Privacy Fence, Vinyl</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>7735</v>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Condo-specific fencing; Falcon estimated $7,735</t>
-        </is>
+          <t>TOTAL OMITTED</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>Retaining Wall, Wood Tie Wells</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>Structural/safety; Falcon estimated $15,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Driveway Seal Coat (recurring 5-yr cycle)</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="n">
-        <v>9473</v>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>Recurring maintenance; Falcon estimated $9,473/cycle</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL OMITTED</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="n">
-        <v>32208</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>Prepared June 2026. Review and update annually.</t>
         </is>
@@ -1755,17 +1631,17 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>300000</v>
+        <v>125000</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>25100</v>
+        <v>23100</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Reach &amp; hold target (worst-case building replacement)</t>
+          <t>Reach &amp; hold target (uninsured structural &amp; shortfall exposure — deductible on HOA)</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>121400</v>
+        <v>111000</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>95000</v>
@@ -1848,7 +1724,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>1435572</v>
+        <v>1304392</v>
       </c>
     </row>
     <row r="20">
@@ -3395,7 +3271,7 @@
         <v/>
       </c>
       <c r="D12" s="15" t="n">
-        <v>223791</v>
+        <v>217535</v>
       </c>
       <c r="E12" s="15">
         <f>B12*'Fund Summary'!$B$8</f>
@@ -3491,7 +3367,7 @@
         <v/>
       </c>
       <c r="D15" s="15" t="n">
-        <v>342150</v>
+        <v>0</v>
       </c>
       <c r="E15" s="15">
         <f>B15*'Fund Summary'!$B$8</f>
@@ -4909,7 +4785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5015,29 +4891,29 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Asphalt Driveways (Condo IV share)</t>
+          <t>Deck Framing &amp; Footings, Wood (Condo IV share)</t>
         </is>
       </c>
       <c r="B7" s="25" t="n">
-        <v>308000</v>
+        <v>440000</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>0.8266</v>
+        <v>0.3679</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>254562</v>
+        <v>64750</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>342150</v>
+        <v>79634</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Deck Framing &amp; Footings, Wood (Condo IV share)</t>
+          <t>Deck Boards (surface), Wood (Condo IV share)</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
@@ -5047,19 +4923,19 @@
         <v>0.3679</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>64750</v>
+        <v>56657</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2033</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>79634</v>
+        <v>69681</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Deck Boards (surface), Wood (Condo IV share)</t>
+          <t>Deck Railings &amp; Balusters, Wood (Condo IV share) (safety)</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
@@ -5069,111 +4945,107 @@
         <v>0.3679</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>56657</v>
+        <v>40469</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>2033</v>
+        <v>2027</v>
       </c>
       <c r="F9" s="25" t="n">
-        <v>69681</v>
+        <v>41683</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Deck Railings &amp; Balusters, Wood (Condo IV share) (safety)</t>
+          <t>Deck Replacement, Composite (Condo IV share)</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
-        <v>440000</v>
+        <v>360000</v>
       </c>
       <c r="C10" s="26" t="n">
         <v>0.3679</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>40469</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>2027</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>41683</v>
+        <v>132444</v>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>2053 (beyond plan)</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Beyond plan horizon</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Deck Replacement, Composite (Condo IV share)</t>
+          <t>Chimney Chase Covers (Condo IV share)</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
-        <v>360000</v>
+        <v>178800</v>
       </c>
       <c r="C11" s="26" t="n">
-        <v>0.3679</v>
+        <v>0.7</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>132444</v>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>2053 (beyond plan)</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Beyond plan horizon</t>
-        </is>
+        <v>125160</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>2031</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>145095</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Chimney Chase Covers (Condo IV share)</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>178800</v>
-      </c>
+          <t>Entry Stoops — Concrete Replacement</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n"/>
       <c r="C12" s="26" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>125160</v>
+        <v>196000</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="F12" s="25" t="n">
-        <v>145095</v>
+        <v>234034</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Concrete Sidewalks (Condo IV share)</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="n">
-        <v>35200</v>
-      </c>
+          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="n"/>
       <c r="C13" s="26" t="n">
-        <v>0.1445</v>
+        <v>1</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>5086</v>
+        <v>29400</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="F13" s="25" t="n">
-        <v>6256</v>
+        <v>31190</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Entry Stoops — Concrete Replacement</t>
+          <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
         </is>
       </c>
       <c r="B14" s="25" t="n"/>
@@ -5181,63 +5053,23 @@
         <v>1</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>196000</v>
+        <v>15000</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>234034</v>
+        <v>15450</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="25" t="n">
-        <v>29400</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>2028</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>31190</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
-        </is>
-      </c>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="25" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>2027</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>15450</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n">
-        <v>3451433</v>
+      <c r="D15" s="8" t="n">
+        <v>3191785</v>
       </c>
     </row>
   </sheetData>
@@ -5252,7 +5084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5267,8 +5099,6 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5306,50 +5136,40 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Asphalt Driveways</t>
+          <t>Chimney Chase Covers</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Chimney Chase Covers</t>
+          <t>Deck Boards (surface)</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Concrete Sidewalks</t>
+          <t>Deck Framing &amp; Footings</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Deck Boards (surface)</t>
+          <t>Deck Railings &amp; Balusters (safety)</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Deck Framing &amp; Footings</t>
+          <t>Entry Stoops — Concrete Replacement</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>Deck Railings &amp; Balusters (safety)</t>
+          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>Entry Stoops — Concrete Replacement</t>
+          <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>Siding, Vinyl</t>
         </is>
@@ -5359,19 +5179,19 @@
       <c r="A3" s="27" t="n"/>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Asphalt Driveways</t>
+          <t>Chimney Chase Covers</t>
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>342150</v>
+        <v>145095</v>
       </c>
       <c r="E3" t="n">
         <v>2027</v>
       </c>
-      <c r="K3" s="28" t="n">
+      <c r="I3" s="28" t="n">
         <v>41683</v>
       </c>
-      <c r="N3" s="28" t="n">
+      <c r="L3" s="28" t="n">
         <v>15450</v>
       </c>
     </row>
@@ -5379,16 +5199,16 @@
       <c r="A4" s="29" t="n"/>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Chimney Chase Covers</t>
+          <t>Deck Boards (surface)</t>
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>145095</v>
+        <v>69680</v>
       </c>
       <c r="E4" t="n">
         <v>2028</v>
       </c>
-      <c r="M4" s="28" t="n">
+      <c r="K4" s="28" t="n">
         <v>31190</v>
       </c>
     </row>
@@ -5396,16 +5216,16 @@
       <c r="A5" s="30" t="n"/>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Concrete Sidewalks</t>
+          <t>Deck Framing &amp; Footings</t>
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>6256</v>
+        <v>79635</v>
       </c>
       <c r="E5" t="n">
         <v>2031</v>
       </c>
-      <c r="G5" s="28" t="n">
+      <c r="F5" s="28" t="n">
         <v>145095</v>
       </c>
     </row>
@@ -5413,16 +5233,16 @@
       <c r="A6" s="31" t="n"/>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Deck Boards (surface)</t>
+          <t>Deck Railings &amp; Balusters (safety)</t>
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>69680</v>
+        <v>162418</v>
       </c>
       <c r="E6" t="n">
         <v>2032</v>
       </c>
-      <c r="L6" s="28" t="n">
+      <c r="J6" s="28" t="n">
         <v>234034</v>
       </c>
     </row>
@@ -5430,28 +5250,25 @@
       <c r="A7" s="32" t="n"/>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Deck Framing &amp; Footings</t>
+          <t>Entry Stoops — Concrete Replacement</t>
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>79635</v>
+        <v>234034</v>
       </c>
       <c r="E7" t="n">
         <v>2033</v>
       </c>
+      <c r="G7" s="28" t="n">
+        <v>69680</v>
+      </c>
       <c r="H7" s="28" t="n">
-        <v>6256</v>
+        <v>79635</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>69680</v>
-      </c>
-      <c r="J7" s="28" t="n">
-        <v>79635</v>
-      </c>
-      <c r="K7" s="28" t="n">
         <v>49772</v>
       </c>
-      <c r="N7" s="28" t="n">
+      <c r="L7" s="28" t="n">
         <v>18448</v>
       </c>
     </row>
@@ -5459,16 +5276,16 @@
       <c r="A8" s="33" t="n"/>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Deck Railings &amp; Balusters (safety)</t>
+          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>162418</v>
+        <v>174751</v>
       </c>
       <c r="E8" t="n">
         <v>2035</v>
       </c>
-      <c r="M8" s="28" t="n">
+      <c r="K8" s="28" t="n">
         <v>38360</v>
       </c>
     </row>
@@ -5476,81 +5293,55 @@
       <c r="A9" s="34" t="n"/>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Entry Stoops — Concrete Replacement</t>
+          <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>234034</v>
+        <v>82229</v>
       </c>
       <c r="E9" t="n">
-        <v>2036</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>342150</v>
+        <v>2039</v>
+      </c>
+      <c r="L9" s="28" t="n">
+        <v>22028</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="n"/>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
+          <t>Siding, Vinyl</t>
         </is>
       </c>
       <c r="C10" s="25" t="n">
-        <v>174751</v>
+        <v>3260083</v>
       </c>
       <c r="E10" t="n">
-        <v>2039</v>
-      </c>
-      <c r="N10" s="28" t="n">
-        <v>22028</v>
+        <v>2042</v>
+      </c>
+      <c r="K10" s="28" t="n">
+        <v>47178</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n"/>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
-        </is>
-      </c>
-      <c r="C11" s="25" t="n">
-        <v>82229</v>
-      </c>
       <c r="E11" t="n">
-        <v>2042</v>
-      </c>
-      <c r="M11" s="28" t="n">
-        <v>47178</v>
+        <v>2045</v>
+      </c>
+      <c r="I11" s="28" t="n">
+        <v>70963</v>
+      </c>
+      <c r="L11" s="28" t="n">
+        <v>26303</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="n"/>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Siding, Vinyl</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="n">
-        <v>3260083</v>
-      </c>
       <c r="E12" t="n">
-        <v>2045</v>
+        <v>2049</v>
       </c>
       <c r="K12" s="28" t="n">
-        <v>70963</v>
-      </c>
-      <c r="N12" s="28" t="n">
-        <v>26303</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="E13" t="n">
-        <v>2049</v>
-      </c>
-      <c r="M13" s="28" t="n">
         <v>58023</v>
       </c>
-      <c r="O13" s="28" t="n">
+      <c r="M12" s="28" t="n">
         <v>3260083</v>
       </c>
     </row>

--- a/Condo_IV_Reserve_Plan.xlsx
+++ b/Condo_IV_Reserve_Plan.xlsx
@@ -67,7 +67,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -134,6 +134,12 @@
         <bgColor rgb="009B57A0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00636363"/>
+        <bgColor rgb="00636363"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -153,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -196,6 +202,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -544,6 +551,33 @@
           <val>
             <numRef>
               <f>'Expenditure Chart'!$M$3:$M$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Expenditure Chart'!N2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="636363"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Expenditure Chart'!$E$3:$E$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Expenditure Chart'!$N$3:$N$12</f>
             </numRef>
           </val>
         </ser>
@@ -930,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E79"/>
+  <dimension ref="B1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -971,7 +1005,7 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>per-unit monthly funding, and the 'Reduction Readiness' gates all on one page.</t>
+          <t>per-unit monthly funding, and the 'Reserve Funding Status' all on one page.</t>
         </is>
       </c>
     </row>
@@ -985,7 +1019,7 @@
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>show that fund's year-by-year balance from 2026 to 2050.</t>
+          <t>show that fund's year-by-year balance from 2027 to 2050.</t>
         </is>
       </c>
     </row>
@@ -1041,14 +1075,14 @@
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Total replacement cost (current dollars): $3,191,785</t>
+          <t>Total replacement cost (current dollars): $3,594,809</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Total reserve cash to allocate (2026): $145,989</t>
+          <t>Total reserve cash to allocate (projected reserve cash at 12/31/2026 (from the 2027 budget)): $176,604</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1096,7 @@
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Planning horizon: 2026-2050 (25 years)</t>
+          <t>Planning horizon: 2027-2050 (24 years)</t>
         </is>
       </c>
     </row>
@@ -1228,42 +1262,42 @@
     <row r="49">
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Reduction Readiness — common charges should NOT be reduced until all three gates PASS:</t>
+          <t>Reserve Funding Status — common charges should NOT be reduced until all three are Funded:</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gate 1 — Emergency Reserve is funded to its target.</t>
+          <t xml:space="preserve">  1 — Emergency Reserve is funded to its target.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gate 2 — Long-Term Maintenance stays at/above $0 every year at the proposed contribution.</t>
+          <t xml:space="preserve">  2 — Long-Term Maintenance stays at/above $0 every year at the proposed contribution.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gate 3 — Operating Reserve stays at/above its floor (multiplier x monthly operating expense).</t>
+          <t xml:space="preserve">  3 — Operating Reserve stays at/above its floor (multiplier x monthly operating expense).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>The 'OVERALL' cell reads ELIGIBLE only when all three pass. To model a reduction, lower a</t>
+          <t>The 'Reduction in common charges' cell says a reduction can be considered only when all three</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>fund's Year-1 Contribution on the Fund Summary sheet and watch the gates.</t>
+          <t>are Funded. To model a reduction, lower a fund's Year-1 Contribution on the Fund Summary sheet.</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1372,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>64750</v>
+        <v>149760</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>2033</v>
@@ -1351,7 +1385,7 @@
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>56657</v>
+        <v>131040</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>2033</v>
@@ -1364,137 +1398,176 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>40469</v>
+        <v>93600</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>2027</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Deck Replacement, Composite (Condo IV share)</t>
+          <t>Deck Railings — 2027 remaining replacements (5 rails)</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
-        <v>132444</v>
+        <v>22500</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2053</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Chimney Chase Covers (Condo IV share)</t>
+          <t>Deck Replacement, Composite (Condo IV share)</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>125160</v>
+        <v>132444</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>2031</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Entry Stoops — Concrete Replacement</t>
+          <t>Chimney Chase Covers (Condo IV share)</t>
         </is>
       </c>
       <c r="C68" s="5" t="n">
-        <v>196000</v>
+        <v>125160</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>2032</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
+          <t>Entry Stoops — Concrete Replacement</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>29400</v>
+        <v>196000</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>2028</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="3" t="inlineStr">
         <is>
+          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>29400</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
           <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
         </is>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C71" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D71" s="3" t="n">
         <v>2027</v>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Items NOT Included (Budget Separately)</t>
-        </is>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Window Wells — rebuild program, 2027 (6 wells)</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>2027</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>The following items from the Falcon 2022 report are NOT in the Becht 2026 study and are therefore NOT included in this funding schedule. Consider budgeting for these items separately.</t>
-        </is>
+          <t>Window Wells — rebuild program, 2028 (15 wells)</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>2028</v>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>Falcon Est. Cost</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Items NOT Included (Budget Separately)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="3" t="inlineStr">
         <is>
+          <t>The following items from the Falcon 2022 report are NOT in the Becht 2026 study and are therefore NOT included in this funding schedule. Consider budgeting for these items separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Falcon Est. Cost</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="3" t="inlineStr">
+        <is>
           <t>Retaining Wall, Wood Tie Wells</t>
         </is>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C79" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>Structural/safety; Falcon estimated $15,000</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="4" t="inlineStr">
+    <row r="80">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>TOTAL OMITTED</t>
         </is>
       </c>
-      <c r="C77" s="7" t="n">
+      <c r="C80" s="7" t="n">
         <v>15000</v>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>Prepared June 2026. Review and update annually.</t>
+    <row r="82">
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Prepared October 2026 (re-based to 2027 to match the 2027 budget). Review and update annually.</t>
         </is>
       </c>
     </row>
@@ -1634,10 +1707,10 @@
         <v>125000</v>
       </c>
       <c r="C12" s="9" t="n">
+        <v>23800</v>
+      </c>
+      <c r="D12" s="9" t="n">
         <v>23100</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -1655,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>111000</v>
+        <v>135100</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>95000</v>
+        <v>91605</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
@@ -1677,10 +1750,10 @@
         <v/>
       </c>
       <c r="C14" s="9" t="n">
-        <v>10400</v>
+        <v>12600</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>50989</v>
+        <v>61899</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -1724,7 +1797,7 @@
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>1304392</v>
+        <v>1484351</v>
       </c>
     </row>
     <row r="20">
@@ -1763,14 +1836,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>REDUCTION READINESS — ALL THREE GATES MUST PASS</t>
+          <t>RESERVE FUNDING STATUS — ALL THREE MUST BE FUNDED BEFORE ANY REDUCTION</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Reserve target</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -1804,7 +1877,7 @@
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IF(D12&gt;=B12,"PASS","FAIL")</f>
+        <f>IF(D12&gt;=B12,"Funded","To be funded")</f>
         <v/>
       </c>
     </row>
@@ -1818,11 +1891,11 @@
         <v>0</v>
       </c>
       <c r="C27" s="15">
-        <f>MIN('Long-Term Maintenance'!F5:F29)</f>
+        <f>MIN('Long-Term Maintenance'!F5:F28)</f>
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>IF(C27&gt;=B27,"PASS","FAIL")</f>
+        <f>IF(C27&gt;=B27,"Funded","To be funded")</f>
         <v/>
       </c>
     </row>
@@ -1837,22 +1910,22 @@
         <v/>
       </c>
       <c r="C28" s="15">
-        <f>MIN('Operating Reserve'!F5:F29)</f>
+        <f>MIN('Operating Reserve'!F5:F28)</f>
         <v/>
       </c>
       <c r="D28" s="17">
-        <f>IF(C28&gt;=B28,"PASS","FAIL")</f>
+        <f>IF(C28&gt;=B28,"Funded","To be funded")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>OVERALL</t>
+          <t>Reduction in common charges</t>
         </is>
       </c>
       <c r="D29" s="18">
-        <f>IF(AND(D26="PASS",D27="PASS",D28="PASS"),"ELIGIBLE TO CONSIDER REDUCTION","NOT ELIGIBLE — HOLD DUES")</f>
+        <f>IF(AND(D26="Funded",D27="Funded",D28="Funded"),"Reduction can be considered","Not yet supported — hold common charges")</f>
         <v/>
       </c>
     </row>
@@ -1877,7 +1950,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>To model a dues reduction: lower a fund's Year-1 Contribution above and watch the gates. Any gate turning FAIL means the reduction is not supported.</t>
+          <t>To model a dues reduction: lower a fund's Year-1 Contribution above and watch the status. Any target turning 'To be funded' means the reduction is not supported.</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1968,7 @@
         </is>
       </c>
       <c r="B37" s="9" t="n">
-        <v>36503</v>
+        <v>39286.67</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2006,34 +2079,34 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="D26">
     <cfRule type="expression" priority="4" dxfId="0">
-      <formula>D26="FAIL"</formula>
+      <formula>D26="To be funded"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="2">
-      <formula>D26="PASS"</formula>
+      <formula>D26="Funded"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27">
     <cfRule type="expression" priority="6" dxfId="0">
-      <formula>D27="FAIL"</formula>
+      <formula>D27="To be funded"</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="2">
-      <formula>D27="PASS"</formula>
+      <formula>D27="Funded"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D28">
     <cfRule type="expression" priority="8" dxfId="0">
-      <formula>D28="FAIL"</formula>
+      <formula>D28="To be funded"</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="2">
-      <formula>D28="PASS"</formula>
+      <formula>D28="Funded"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D29">
     <cfRule type="expression" priority="10" dxfId="0">
-      <formula>ISNUMBER(SEARCH("NOT",D29))</formula>
+      <formula>ISNUMBER(SEARCH("NOT YET",D29))</formula>
     </cfRule>
     <cfRule type="expression" priority="11" dxfId="2">
-      <formula>ISNUMBER(SEARCH("CONSIDER",D29))</formula>
+      <formula>ISNUMBER(SEARCH("CONSIDERED",D29))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2047,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2128,7 +2201,7 @@
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B5" s="15">
         <f>'Fund Summary'!$D$12</f>
@@ -2160,7 +2233,7 @@
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B6" s="15">
         <f>F5</f>
@@ -2192,7 +2265,7 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B7" s="15">
         <f>F6</f>
@@ -2224,7 +2297,7 @@
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B8" s="15">
         <f>F7</f>
@@ -2256,7 +2329,7 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B9" s="15">
         <f>F8</f>
@@ -2288,7 +2361,7 @@
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B10" s="15">
         <f>F9</f>
@@ -2320,7 +2393,7 @@
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="B11" s="15">
         <f>F10</f>
@@ -2352,7 +2425,7 @@
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B12" s="15">
         <f>F11</f>
@@ -2384,7 +2457,7 @@
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B13" s="15">
         <f>F12</f>
@@ -2416,7 +2489,7 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B14" s="15">
         <f>F13</f>
@@ -2448,7 +2521,7 @@
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="B15" s="15">
         <f>F14</f>
@@ -2480,7 +2553,7 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B16" s="15">
         <f>F15</f>
@@ -2512,7 +2585,7 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B17" s="15">
         <f>F16</f>
@@ -2544,7 +2617,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B18" s="15">
         <f>F17</f>
@@ -2576,7 +2649,7 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="B19" s="15">
         <f>F18</f>
@@ -2608,7 +2681,7 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B20" s="15">
         <f>F19</f>
@@ -2640,7 +2713,7 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B21" s="15">
         <f>F20</f>
@@ -2672,7 +2745,7 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="B22" s="15">
         <f>F21</f>
@@ -2704,7 +2777,7 @@
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B23" s="15">
         <f>F22</f>
@@ -2736,7 +2809,7 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="B24" s="15">
         <f>F23</f>
@@ -2768,7 +2841,7 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B25" s="15">
         <f>F24</f>
@@ -2800,7 +2873,7 @@
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="B26" s="15">
         <f>F25</f>
@@ -2832,7 +2905,7 @@
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B27" s="15">
         <f>F26</f>
@@ -2864,7 +2937,7 @@
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B28" s="15">
         <f>F27</f>
@@ -2895,58 +2968,26 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n">
-        <v>2050</v>
-      </c>
-      <c r="B29" s="15">
-        <f>F28</f>
-        <v/>
-      </c>
-      <c r="C29" s="15">
-        <f>IF(F28&gt;='Fund Summary'!$B$12,0,'Fund Summary'!$C$12*(1+'Fund Summary'!$B$7)^24)</f>
-        <v/>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="15">
-        <f>B29*'Fund Summary'!$B$8</f>
-        <v/>
-      </c>
-      <c r="F29" s="15">
-        <f>B29+C29-D29+E29</f>
-        <v/>
-      </c>
-      <c r="G29" s="24">
-        <f>C29/'Fund Summary'!$B$6/12</f>
-        <v/>
-      </c>
-      <c r="H29" s="17">
-        <f>IF(F29&gt;='Fund Summary'!$B$12,"FUNDED","BUILDING")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C30" s="8">
-        <f>SUM(C5:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="8">
-        <f>SUM(D5:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="8">
-        <f>SUM(E5:E29)</f>
+      <c r="C29" s="8">
+        <f>SUM(C5:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="8">
+        <f>SUM(D5:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="8">
+        <f>SUM(E5:E28)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F5:F29">
+  <conditionalFormatting sqref="F5:F28">
     <cfRule type="expression" priority="1" dxfId="2">
       <formula>F5&gt;=$J$2</formula>
     </cfRule>
@@ -2965,7 +3006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3036,7 +3077,7 @@
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B5" s="15">
         <f>'Fund Summary'!$D$13</f>
@@ -3047,7 +3088,7 @@
         <v/>
       </c>
       <c r="D5" s="15" t="n">
-        <v>0</v>
+        <v>88065</v>
       </c>
       <c r="E5" s="15">
         <f>B5*'Fund Summary'!$B$8</f>
@@ -3068,7 +3109,7 @@
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B6" s="15">
         <f>F5</f>
@@ -3079,7 +3120,7 @@
         <v/>
       </c>
       <c r="D6" s="15" t="n">
-        <v>57133</v>
+        <v>158498</v>
       </c>
       <c r="E6" s="15">
         <f>B6*'Fund Summary'!$B$8</f>
@@ -3100,7 +3141,7 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B7" s="15">
         <f>F6</f>
@@ -3111,7 +3152,7 @@
         <v/>
       </c>
       <c r="D7" s="15" t="n">
-        <v>31190</v>
+        <v>0</v>
       </c>
       <c r="E7" s="15">
         <f>B7*'Fund Summary'!$B$8</f>
@@ -3132,7 +3173,7 @@
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B8" s="15">
         <f>F7</f>
@@ -3164,7 +3205,7 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B9" s="15">
         <f>F8</f>
@@ -3175,7 +3216,7 @@
         <v/>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0</v>
+        <v>145095</v>
       </c>
       <c r="E9" s="15">
         <f>B9*'Fund Summary'!$B$8</f>
@@ -3196,7 +3237,7 @@
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B10" s="15">
         <f>F9</f>
@@ -3207,7 +3248,7 @@
         <v/>
       </c>
       <c r="D10" s="15" t="n">
-        <v>145095</v>
+        <v>234034</v>
       </c>
       <c r="E10" s="15">
         <f>B10*'Fund Summary'!$B$8</f>
@@ -3228,7 +3269,7 @@
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="B11" s="15">
         <f>F10</f>
@@ -3239,7 +3280,7 @@
         <v/>
       </c>
       <c r="D11" s="15" t="n">
-        <v>234034</v>
+        <v>478913</v>
       </c>
       <c r="E11" s="15">
         <f>B11*'Fund Summary'!$B$8</f>
@@ -3260,7 +3301,7 @@
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B12" s="15">
         <f>F11</f>
@@ -3271,7 +3312,7 @@
         <v/>
       </c>
       <c r="D12" s="15" t="n">
-        <v>217535</v>
+        <v>0</v>
       </c>
       <c r="E12" s="15">
         <f>B12*'Fund Summary'!$B$8</f>
@@ -3292,7 +3333,7 @@
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B13" s="15">
         <f>F12</f>
@@ -3303,7 +3344,7 @@
         <v/>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0</v>
+        <v>38360</v>
       </c>
       <c r="E13" s="15">
         <f>B13*'Fund Summary'!$B$8</f>
@@ -3324,7 +3365,7 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B14" s="15">
         <f>F13</f>
@@ -3335,7 +3376,7 @@
         <v/>
       </c>
       <c r="D14" s="15" t="n">
-        <v>38360</v>
+        <v>0</v>
       </c>
       <c r="E14" s="15">
         <f>B14*'Fund Summary'!$B$8</f>
@@ -3356,7 +3397,7 @@
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="B15" s="15">
         <f>F14</f>
@@ -3388,7 +3429,7 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B16" s="15">
         <f>F15</f>
@@ -3420,7 +3461,7 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B17" s="15">
         <f>F16</f>
@@ -3431,7 +3472,7 @@
         <v/>
       </c>
       <c r="D17" s="15" t="n">
-        <v>0</v>
+        <v>22028</v>
       </c>
       <c r="E17" s="15">
         <f>B17*'Fund Summary'!$B$8</f>
@@ -3452,7 +3493,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B18" s="15">
         <f>F17</f>
@@ -3463,7 +3504,7 @@
         <v/>
       </c>
       <c r="D18" s="15" t="n">
-        <v>22028</v>
+        <v>0</v>
       </c>
       <c r="E18" s="15">
         <f>B18*'Fund Summary'!$B$8</f>
@@ -3484,7 +3525,7 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="B19" s="15">
         <f>F18</f>
@@ -3516,7 +3557,7 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B20" s="15">
         <f>F19</f>
@@ -3527,7 +3568,7 @@
         <v/>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0</v>
+        <v>47178</v>
       </c>
       <c r="E20" s="15">
         <f>B20*'Fund Summary'!$B$8</f>
@@ -3548,7 +3589,7 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B21" s="15">
         <f>F20</f>
@@ -3559,7 +3600,7 @@
         <v/>
       </c>
       <c r="D21" s="15" t="n">
-        <v>47178</v>
+        <v>0</v>
       </c>
       <c r="E21" s="15">
         <f>B21*'Fund Summary'!$B$8</f>
@@ -3580,7 +3621,7 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="B22" s="15">
         <f>F21</f>
@@ -3612,7 +3653,7 @@
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B23" s="15">
         <f>F22</f>
@@ -3623,7 +3664,7 @@
         <v/>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0</v>
+        <v>190431</v>
       </c>
       <c r="E23" s="15">
         <f>B23*'Fund Summary'!$B$8</f>
@@ -3644,7 +3685,7 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="B24" s="15">
         <f>F23</f>
@@ -3655,7 +3696,7 @@
         <v/>
       </c>
       <c r="D24" s="15" t="n">
-        <v>97266</v>
+        <v>0</v>
       </c>
       <c r="E24" s="15">
         <f>B24*'Fund Summary'!$B$8</f>
@@ -3676,7 +3717,7 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B25" s="15">
         <f>F24</f>
@@ -3708,7 +3749,7 @@
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="B26" s="15">
         <f>F25</f>
@@ -3740,7 +3781,7 @@
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B27" s="15">
         <f>F26</f>
@@ -3751,7 +3792,7 @@
         <v/>
       </c>
       <c r="D27" s="15" t="n">
-        <v>0</v>
+        <v>3318106</v>
       </c>
       <c r="E27" s="15">
         <f>B27*'Fund Summary'!$B$8</f>
@@ -3772,7 +3813,7 @@
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B28" s="15">
         <f>F27</f>
@@ -3783,7 +3824,7 @@
         <v/>
       </c>
       <c r="D28" s="15" t="n">
-        <v>3318106</v>
+        <v>0</v>
       </c>
       <c r="E28" s="15">
         <f>B28*'Fund Summary'!$B$8</f>
@@ -3803,58 +3844,26 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n">
-        <v>2050</v>
-      </c>
-      <c r="B29" s="15">
-        <f>F28</f>
-        <v/>
-      </c>
-      <c r="C29" s="15">
-        <f>C28*(1+'Fund Summary'!$B$7)</f>
-        <v/>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="15">
-        <f>B29*'Fund Summary'!$B$8</f>
-        <v/>
-      </c>
-      <c r="F29" s="15">
-        <f>B29+C29-D29+E29</f>
-        <v/>
-      </c>
-      <c r="G29" s="24">
-        <f>C29/'Fund Summary'!$B$6/12</f>
-        <v/>
-      </c>
-      <c r="H29" s="17">
-        <f>IF(F29&lt;0,"BELOW $0","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C30" s="8">
-        <f>SUM(C5:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="8">
-        <f>SUM(D5:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="8">
-        <f>SUM(E5:E29)</f>
+      <c r="C29" s="8">
+        <f>SUM(C5:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="8">
+        <f>SUM(D5:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="8">
+        <f>SUM(E5:E28)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F5:F29">
+  <conditionalFormatting sqref="F5:F28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5&lt;0</formula>
     </cfRule>
@@ -3870,7 +3879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3951,7 +3960,7 @@
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B5" s="15">
         <f>'Fund Summary'!$D$14</f>
@@ -3983,7 +3992,7 @@
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B6" s="15">
         <f>F5</f>
@@ -4015,7 +4024,7 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B7" s="15">
         <f>F6</f>
@@ -4047,7 +4056,7 @@
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B8" s="15">
         <f>F7</f>
@@ -4079,7 +4088,7 @@
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B9" s="15">
         <f>F8</f>
@@ -4111,7 +4120,7 @@
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B10" s="15">
         <f>F9</f>
@@ -4143,7 +4152,7 @@
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="B11" s="15">
         <f>F10</f>
@@ -4175,7 +4184,7 @@
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B12" s="15">
         <f>F11</f>
@@ -4207,7 +4216,7 @@
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B13" s="15">
         <f>F12</f>
@@ -4239,7 +4248,7 @@
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B14" s="15">
         <f>F13</f>
@@ -4271,7 +4280,7 @@
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="B15" s="15">
         <f>F14</f>
@@ -4303,7 +4312,7 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B16" s="15">
         <f>F15</f>
@@ -4335,7 +4344,7 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B17" s="15">
         <f>F16</f>
@@ -4367,7 +4376,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B18" s="15">
         <f>F17</f>
@@ -4399,7 +4408,7 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="n">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="B19" s="15">
         <f>F18</f>
@@ -4431,7 +4440,7 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B20" s="15">
         <f>F19</f>
@@ -4463,7 +4472,7 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B21" s="15">
         <f>F20</f>
@@ -4495,7 +4504,7 @@
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="B22" s="15">
         <f>F21</f>
@@ -4527,7 +4536,7 @@
     </row>
     <row r="23">
       <c r="A23" s="12" t="n">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B23" s="15">
         <f>F22</f>
@@ -4559,7 +4568,7 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="B24" s="15">
         <f>F23</f>
@@ -4591,7 +4600,7 @@
     </row>
     <row r="25">
       <c r="A25" s="12" t="n">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B25" s="15">
         <f>F24</f>
@@ -4623,7 +4632,7 @@
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="B26" s="15">
         <f>F25</f>
@@ -4655,7 +4664,7 @@
     </row>
     <row r="27">
       <c r="A27" s="12" t="n">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B27" s="15">
         <f>F26</f>
@@ -4687,7 +4696,7 @@
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B28" s="15">
         <f>F27</f>
@@ -4718,58 +4727,26 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n">
-        <v>2050</v>
-      </c>
-      <c r="B29" s="15">
-        <f>F28</f>
-        <v/>
-      </c>
-      <c r="C29" s="15">
-        <f>IF(F28&gt;='Fund Summary'!$B$14,0,'Fund Summary'!$C$14*(1+'Fund Summary'!$B$7)^24)</f>
-        <v/>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="15">
-        <f>B29*'Fund Summary'!$B$8</f>
-        <v/>
-      </c>
-      <c r="F29" s="15">
-        <f>B29+C29-D29+E29</f>
-        <v/>
-      </c>
-      <c r="G29" s="24">
-        <f>C29/'Fund Summary'!$B$6/12</f>
-        <v/>
-      </c>
-      <c r="H29" s="17">
-        <f>IF(F29&lt;'Fund Summary'!$B$14,"BELOW FLOOR","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C30" s="8">
-        <f>SUM(C5:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="8">
-        <f>SUM(D5:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="8">
-        <f>SUM(E5:E29)</f>
+      <c r="C29" s="8">
+        <f>SUM(C5:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="8">
+        <f>SUM(D5:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="8">
+        <f>SUM(E5:E28)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F5:F29">
+  <conditionalFormatting sqref="F5:F28">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5&lt;$J$2</formula>
     </cfRule>
@@ -4785,7 +4762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4901,13 +4878,13 @@
         <v>0.3679</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>64750</v>
+        <v>149760</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>2033</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>79634</v>
+        <v>184186</v>
       </c>
     </row>
     <row r="8">
@@ -4923,13 +4900,13 @@
         <v>0.3679</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>56657</v>
+        <v>131040</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2033</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>69681</v>
+        <v>161163</v>
       </c>
     </row>
     <row r="9">
@@ -4945,87 +4922,87 @@
         <v>0.3679</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>40469</v>
+        <v>93600</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>2027</v>
+        <v>2033</v>
       </c>
       <c r="F9" s="25" t="n">
-        <v>41683</v>
+        <v>115116</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Deck Replacement, Composite (Condo IV share)</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="n">
-        <v>360000</v>
-      </c>
+          <t>Deck Railings — 2027 remaining replacements (5 rails)</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="n"/>
       <c r="C10" s="26" t="n">
-        <v>0.3679</v>
+        <v>1</v>
       </c>
       <c r="D10" s="25" t="n">
-        <v>132444</v>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>2053 (beyond plan)</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Beyond plan horizon</t>
-        </is>
+        <v>22500</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>2027</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>23175</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Chimney Chase Covers (Condo IV share)</t>
+          <t>Deck Replacement, Composite (Condo IV share)</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
-        <v>178800</v>
+        <v>360000</v>
       </c>
       <c r="C11" s="26" t="n">
-        <v>0.7</v>
+        <v>0.3679</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>125160</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>2031</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>145095</v>
+        <v>132444</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>2053 (beyond plan)</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Beyond plan horizon</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Entry Stoops — Concrete Replacement</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n"/>
+          <t>Chimney Chase Covers (Condo IV share)</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>178800</v>
+      </c>
       <c r="C12" s="26" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>196000</v>
+        <v>125160</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="F12" s="25" t="n">
-        <v>234034</v>
+        <v>145095</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
+          <t>Entry Stoops — Concrete Replacement</t>
         </is>
       </c>
       <c r="B13" s="25" t="n"/>
@@ -5033,19 +5010,19 @@
         <v>1</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>29400</v>
+        <v>196000</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>2028</v>
+        <v>2032</v>
       </c>
       <c r="F13" s="25" t="n">
-        <v>31190</v>
+        <v>234034</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
+          <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
         </is>
       </c>
       <c r="B14" s="25" t="n"/>
@@ -5053,23 +5030,83 @@
         <v>1</v>
       </c>
       <c r="D14" s="25" t="n">
+        <v>29400</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>31190</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="25" t="n">
         <v>15000</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>2027</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F15" s="25" t="n">
         <v>15450</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Window Wells — rebuild program, 2027 (6 wells)</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>2027</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>49440</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Window Wells — rebuild program, 2028 (15 wells)</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="25" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>127308</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
-        <v>3191785</v>
+      <c r="D18" s="8" t="n">
+        <v>3594809</v>
       </c>
     </row>
   </sheetData>
@@ -5084,7 +5121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5099,6 +5136,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5174,6 +5212,11 @@
           <t>Siding, Vinyl</t>
         </is>
       </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>Window Wells (rebuild program)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="27" t="n"/>
@@ -5189,10 +5232,13 @@
         <v>2027</v>
       </c>
       <c r="I3" s="28" t="n">
-        <v>41683</v>
+        <v>23175</v>
       </c>
       <c r="L3" s="28" t="n">
         <v>15450</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>49440</v>
       </c>
     </row>
     <row r="4">
@@ -5203,13 +5249,16 @@
         </is>
       </c>
       <c r="C4" s="25" t="n">
-        <v>69680</v>
+        <v>161163</v>
       </c>
       <c r="E4" t="n">
         <v>2028</v>
       </c>
       <c r="K4" s="28" t="n">
         <v>31190</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>127308</v>
       </c>
     </row>
     <row r="5">
@@ -5220,7 +5269,7 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>79635</v>
+        <v>184186</v>
       </c>
       <c r="E5" t="n">
         <v>2031</v>
@@ -5237,7 +5286,7 @@
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>162418</v>
+        <v>302419</v>
       </c>
       <c r="E6" t="n">
         <v>2032</v>
@@ -5260,13 +5309,13 @@
         <v>2033</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>69680</v>
+        <v>161163</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>79635</v>
+        <v>184186</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>49772</v>
+        <v>115116</v>
       </c>
       <c r="L7" s="28" t="n">
         <v>18448</v>
@@ -5324,11 +5373,20 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" s="36" t="n"/>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Window Wells (rebuild program)</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>176748</v>
+      </c>
       <c r="E11" t="n">
         <v>2045</v>
       </c>
       <c r="I11" s="28" t="n">
-        <v>70963</v>
+        <v>164128</v>
       </c>
       <c r="L11" s="28" t="n">
         <v>26303</v>

--- a/Condo_IV_Reserve_Plan.xlsx
+++ b/Condo_IV_Reserve_Plan.xlsx
@@ -47,18 +47,18 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -165,34 +165,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -964,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E82"/>
+  <dimension ref="B1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -988,584 +988,591 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Unaudited planning estimates. This plan is not a financial statement, is not prepared in accordance with U.S. GAAP, and is not a reserve study under the CAI National Reserve Study Standards. Future costs, timing and balances are estimates and will differ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>How to read this workbook</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>START on the 'Fund Summary' tab — it shows the three funds, their targets/floors, the</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>per-unit monthly funding, and the 'Reserve Funding Status' all on one page.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>The three fund tabs — Emergency Reserve, Long-Term Maintenance, Operating Reserve — each</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>show that fund's year-by-year balance from 2027 to 2050.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>'Components' lists every capital item and its cost; 'Expenditure Chart' plots spending by year.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Yellow cells are inputs you can edit; every other cell is calculated automatically.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Data Sources:</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Based on Becht Engineering Capital Reserve Study (Project 25-1140, February 2026)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Entity allocations derived from Falcon Group Report (2022) per-entity quantity ratios</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Number of units: 98</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Total replacement cost (current dollars): $3,594,809</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Total reserve cash to allocate (projected reserve cash at 12/31/2026 (from the 2027 budget)): $176,604</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Fund contributions are solved automatically (see Fund Summary) and are fully editable.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Planning horizon: 2027-2050 (24 years)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Funding Model Assumptions</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Annual contributions grow at a configurable rate (default 3%) to keep pace with inflation.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Reserve funds earn interest at a configurable rate (default 1%) annually.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Disbursements (expenditures) occur in the year projected by the Becht engineering study.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>All disbursement amounts include 3% annual inflation applied to current replacement costs.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Three-Fund Model</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>This plan splits reserves into THREE decoupled funds, each with its own balance,</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>annual contribution, floor, and monthly cost per unit. Each has its own tab.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr"/>
-    </row>
     <row r="33">
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>1. Emergency Reserve — self-funded buffer for uninsured structural &amp; shortfall exposure — deductible on HOA.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   Floor = a target you set (Fund Summary, yellow cell). Not drawn for routine work.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>2. Long-Term Maintenance — the Becht/Falcon capital replacement schedule.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="3" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   Floor = must NEVER drop below $0 in any year.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="3" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>3. Operating Reserve — decoupled buffer of operating expenses.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="3" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   Floor = multiplier (1-3 months) x monthly operating expense, both set on Fund Summary.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="3" t="inlineStr"/>
-    </row>
     <row r="40">
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Fund Summary sheet: set all inputs here (each fund's starting balance, target/floor and</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="3" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>contribution; unit count; growth; interest). Allocate current cash across the three funds'</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="3" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>starting balances (Allocated Start column). Recommended: fund near-term Long-Term Maintenance</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>needs and Operating liquidity first, and build the Emergency Reserve from contributions.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="3" t="inlineStr"/>
-    </row>
     <row r="45">
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Percent Funded (Long-Term Maintenance) = reserve on hand / Fully Funded Balance. It is</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="3" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>the industry (CAI) metric: under 30% = weak (high special-assessment risk), 30-70% = fair,</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="3" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>70%+ = strong.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="3" t="inlineStr"/>
-    </row>
     <row r="49">
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Reserve Funding Status — common charges should NOT be reduced until all three are Funded:</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="3" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  1 — Emergency Reserve is funded to its target.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  2 — Long-Term Maintenance stays at/above $0 every year at the proposed contribution.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="3" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  3 — Operating Reserve stays at/above its floor (multiplier x monthly operating expense).</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="3" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>The 'Reduction in common charges' cell says a reduction can be considered only when all three</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="3" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>are Funded. To model a reduction, lower a fund's Year-1 Contribution on the Fund Summary sheet.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="3" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Replace every yellow placeholder (targets, floors, total cash) with the entity's ACTUALS.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Components Covered by This Plan</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="3" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>See the 'Components' sheet for full detail. Summary:</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="4" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Allocated Cost</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Replacement Year</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="3" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Siding, Vinyl (Condo IV share)</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="6" t="n">
         <v>1651860</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="D62" s="4" t="n">
         <v>2049</v>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="3" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Roof, Shingles - Townhouses (Condo IV share)</t>
         </is>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C63" s="6" t="n">
         <v>880045</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="D63" s="4" t="n">
         <v>2050</v>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="3" t="inlineStr">
+    <row r="64">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Deck Framing &amp; Footings, Wood (Condo IV share)</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C64" s="6" t="n">
         <v>149760</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D64" s="4" t="n">
         <v>2033</v>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="3" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Deck Boards (surface), Wood (Condo IV share)</t>
         </is>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C65" s="6" t="n">
         <v>131040</v>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D65" s="4" t="n">
         <v>2033</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="3" t="inlineStr">
+    <row r="66">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Deck Railings &amp; Balusters, Wood (Condo IV share) (safety)</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C66" s="6" t="n">
         <v>93600</v>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="D66" s="4" t="n">
         <v>2033</v>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="3" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Deck Railings — 2027 remaining replacements (5 rails)</t>
         </is>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C67" s="6" t="n">
         <v>22500</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D67" s="4" t="n">
         <v>2027</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="3" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Deck Replacement, Composite (Condo IV share)</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C68" s="6" t="n">
         <v>132444</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D68" s="4" t="n">
         <v>2053</v>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="3" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Chimney Chase Covers (Condo IV share)</t>
         </is>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C69" s="6" t="n">
         <v>125160</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D69" s="4" t="n">
         <v>2031</v>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="3" t="inlineStr">
+    <row r="70">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>Entry Stoops — Concrete Replacement</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C70" s="6" t="n">
         <v>196000</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D70" s="4" t="n">
         <v>2032</v>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="3" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
         </is>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C71" s="6" t="n">
         <v>29400</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D71" s="4" t="n">
         <v>2028</v>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="3" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
         </is>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C72" s="6" t="n">
         <v>15000</v>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D72" s="4" t="n">
         <v>2027</v>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="3" t="inlineStr">
+    <row r="73">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>Window Wells — rebuild program, 2027 (6 wells)</t>
         </is>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C73" s="6" t="n">
         <v>48000</v>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="D73" s="4" t="n">
         <v>2027</v>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="3" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Window Wells — rebuild program, 2028 (15 wells)</t>
         </is>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C74" s="6" t="n">
         <v>120000</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D74" s="4" t="n">
         <v>2028</v>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Items NOT Included (Budget Separately)</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="3" t="inlineStr">
+    <row r="77">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>The following items from the Falcon 2022 report are NOT in the Becht 2026 study and are therefore NOT included in this funding schedule. Consider budgeting for these items separately.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="4" t="inlineStr">
+    <row r="79">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>Falcon Est. Cost</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>Retaining Wall, Wood Tie Wells</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>Structural/safety; Falcon estimated $15,000</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="4" t="inlineStr">
         <is>
+          <t>Retaining Wall, Wood Tie Wells</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Structural/safety; Falcon estimated $15,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="5" t="inlineStr">
+        <is>
           <t>TOTAL OMITTED</t>
         </is>
       </c>
-      <c r="C80" s="7" t="n">
+      <c r="C81" s="7" t="n">
         <v>15000</v>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="6" t="inlineStr">
+    <row r="83">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>Prepared October 2026 (re-based to 2027 to match the 2027 budget). Review and update annually.</t>
         </is>
@@ -1604,9 +1611,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Three decoupled funds. Yellow cells are inputs — replace placeholders with actual figures.</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Three decoupled funds. Yellow cells are inputs — replace placeholders with actual figures. Unaudited planning estimates; not a GAAP financial statement.</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1625,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Total Reserve Cash (all accounts):</t>
         </is>
@@ -1627,14 +1634,14 @@
         <f>SUM(D12:D14)</f>
         <v/>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Auto-total of the three fund starting balances (Allocated Start column).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Number of Units:</t>
         </is>
@@ -1644,7 +1651,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Contribution Growth Rate:</t>
         </is>
@@ -1654,7 +1661,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Interest Rate on Reserves:</t>
         </is>
@@ -1777,7 +1784,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Allocated Start = each fund's current balance (yellow, editable); Total Reserve Cash (B5) is their sum. Recommended: fund near-term Long-Term Maintenance and Operating liquidity first, and build the Emergency Reserve from contributions over time.</t>
         </is>
@@ -1791,7 +1798,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Fully Funded Balance (FFB — what LTM should hold today):</t>
         </is>
@@ -1801,7 +1808,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>LTM Reserve (allocated start):</t>
         </is>
@@ -1812,7 +1819,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Percent Funded:</t>
         </is>
@@ -1821,13 +1828,13 @@
         <f>IF(B19=0,0,B20/B19)</f>
         <v/>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="4">
         <f>IF(B21&lt;0.3,"WEAK (&lt;30% - high special-assessment risk)",IF(B21&lt;0.7,"FAIR (30-70%)","STRONG (70%+)"))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>CAI bands: under 30% = weak; 30-70% = fair; 70%+ = strong.</t>
         </is>
@@ -1930,7 +1937,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Combined Monthly Cost per Unit (Year 1, all three funds):</t>
         </is>
@@ -1941,14 +1948,14 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Grows at the Growth Rate each year; this is Year-1. Add the HOA per-unit amount for a unit owner's all-in monthly.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>To model a dues reduction: lower a fund's Year-1 Contribution above and watch the status. Any target turning 'To be funded' means the reduction is not supported.</t>
         </is>
@@ -1962,7 +1969,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Monthly Operating Expense:</t>
         </is>
@@ -1970,14 +1977,14 @@
       <c r="B37" s="9" t="n">
         <v>39286.67</v>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>The association's total monthly operating spend (excludes reserve contributions).</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Operating Reserve Multiplier (months, 1-3):</t>
         </is>
@@ -1985,7 +1992,7 @@
       <c r="B38" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Operating Reserve floor (row 14) = this multiplier x monthly operating expense.</t>
         </is>
@@ -2055,7 +2062,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Equal per-unit split (fund contribution / units / 12); grows ~3%/yr. Excludes the separate $365/unit HOA dues. If common charges are set by percentage interest, larger units pay proportionally more than this average.</t>
         </is>
@@ -2140,14 +2147,14 @@
           <t>Scarborough Glen Condo Association IV — Emergency Reserve</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Floor (from Fund Summary):</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>All inputs are set on the Fund Summary sheet. This tab is calculated.</t>
         </is>
@@ -3027,7 +3034,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>All inputs are set on the Fund Summary sheet. This tab is calculated.</t>
         </is>
@@ -3899,14 +3906,14 @@
           <t>Scarborough Glen Condo Association IV — Operating Reserve</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Floor (from Fund Summary):</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>All inputs are set on the Fund Summary sheet. This tab is calculated.</t>
         </is>
@@ -4781,7 +4788,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>All costs from Becht Engineering Capital Reserve Study (2026)</t>
         </is>
@@ -5152,67 +5159,67 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>25-Year Total</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Chimney Chase Covers</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Deck Boards (surface)</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Deck Framing &amp; Footings</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Deck Railings &amp; Balusters (safety)</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Entry Stoops — Concrete Replacement</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Entry Stoops — Leveling &amp; Stair Nosing (safety)</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Exterior Caulk/Sealant &amp; Trim Maintenance</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>Siding, Vinyl</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>Window Wells (rebuild program)</t>
         </is>
